--- a/output/mainline_sectors.xlsx
+++ b/output/mainline_sectors.xlsx
@@ -58,12 +58,12 @@
     <t>通用设备</t>
   </si>
   <si>
+    <t>光学光电子</t>
+  </si>
+  <si>
     <t>专用设备</t>
   </si>
   <si>
-    <t>光学光电子</t>
-  </si>
-  <si>
     <t>火力发电</t>
   </si>
   <si>
@@ -73,41 +73,33 @@
     <t>机床工具</t>
   </si>
   <si>
+    <t>面板</t>
+  </si>
+  <si>
     <t>能源及重型设备</t>
   </si>
   <si>
-    <t>面板</t>
-  </si>
-  <si>
-    <t>绿发电力,建投能源,节能风电,韶能股份,广西能源,大唐发电,华银电力,豫能控股,兆新股份,华电辽能</t>
-  </si>
-  <si>
-    <t>中超控股,汉缆股份,中电鑫龙,泽宇智能,长城科技,华通线缆,白云电器,安靠智电,起帆电缆,中国西电</t>
-  </si>
-  <si>
-    <t>宗申动力,正泰电源,凤形股份,中寰股份,海鸥股份,新柴股份,开山股份,泰嘉股份,新锦动力,大元泵业</t>
-  </si>
-  <si>
-    <t>标准股份,电光科技,展鹏科技,山东墨龙,深科达,天鹅股份,德石股份,卓郎智能,凯格精机,强瑞技术</t>
-  </si>
-  <si>
-    <t>奥瑞德,联建光电,华映科技,深纺织Ａ,晨丰科技,同兴达,纬达光电,芯瑞达,亚世光电,深华发Ａ</t>
+    <t>大唐发电,粤电力Ａ,迪森股份,江苏新能,赣能股份,拓日新能,深南电A,华光环能,华电能源,华电辽能</t>
+  </si>
+  <si>
+    <t>长城电工,新宏泰,百利电气,汉缆股份,中超控股,新能泰山,神马电力,正泰电器,三晖电气,白云电器</t>
+  </si>
+  <si>
+    <t>正泰电源,宇环数控,威星智能,宁波精达,亚威股份,新锦动力,日发精机,川润股份,海鸥股份,永和智控</t>
+  </si>
+  <si>
+    <t>华灿光电,联建光电,聚灿光电,瑞丰光电,深纺织Ａ,奥瑞德,纬达光电,晨丰科技,聚飞光电,国星光电</t>
+  </si>
+  <si>
+    <t>标准股份,卓郎智能,泰坦股份,合锻智能,凯格精机,电光科技,长江能科,神开股份,锡装股份,同力天启</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -123,7 +115,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -131,30 +123,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -453,25 +427,25 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -486,13 +460,13 @@
         <v>16</v>
       </c>
       <c r="D2">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F2">
-        <v>3.05</v>
+        <v>4.05</v>
       </c>
       <c r="G2" t="s">
         <v>21</v>
@@ -509,13 +483,13 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F3">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="G3" t="s">
         <v>22</v>
@@ -532,13 +506,13 @@
         <v>18</v>
       </c>
       <c r="D4">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E4">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F4">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="G4" t="s">
         <v>23</v>
@@ -546,7 +520,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -555,13 +529,13 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F5">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="G5" t="s">
         <v>24</v>
@@ -569,7 +543,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
@@ -578,13 +552,13 @@
         <v>20</v>
       </c>
       <c r="D6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="G6" t="s">
         <v>25</v>

--- a/output/mainline_sectors.xlsx
+++ b/output/mainline_sectors.xlsx
@@ -58,12 +58,12 @@
     <t>通用设备</t>
   </si>
   <si>
+    <t>专用设备</t>
+  </si>
+  <si>
     <t>光学光电子</t>
   </si>
   <si>
-    <t>专用设备</t>
-  </si>
-  <si>
     <t>火力发电</t>
   </si>
   <si>
@@ -73,25 +73,25 @@
     <t>机床工具</t>
   </si>
   <si>
+    <t>能源及重型设备</t>
+  </si>
+  <si>
     <t>面板</t>
   </si>
   <si>
-    <t>能源及重型设备</t>
-  </si>
-  <si>
-    <t>大唐发电,粤电力Ａ,迪森股份,江苏新能,赣能股份,拓日新能,深南电A,华光环能,华电能源,华电辽能</t>
-  </si>
-  <si>
-    <t>长城电工,新宏泰,百利电气,汉缆股份,中超控股,新能泰山,神马电力,正泰电器,三晖电气,白云电器</t>
-  </si>
-  <si>
-    <t>正泰电源,宇环数控,威星智能,宁波精达,亚威股份,新锦动力,日发精机,川润股份,海鸥股份,永和智控</t>
-  </si>
-  <si>
-    <t>华灿光电,联建光电,聚灿光电,瑞丰光电,深纺织Ａ,奥瑞德,纬达光电,晨丰科技,聚飞光电,国星光电</t>
-  </si>
-  <si>
-    <t>标准股份,卓郎智能,泰坦股份,合锻智能,凯格精机,电光科技,长江能科,神开股份,锡装股份,同力天启</t>
+    <t>华电辽能,节能风电,通宝能源,粤电力Ａ,华电能源,闽东电力,华光环能,建投能源,晶科科技,富春环保</t>
+  </si>
+  <si>
+    <t>中国西电,汉缆股份,华盛昌,新能泰山,新宏泰,国电南自,迦南智能,三变科技,中电鑫龙,正泰电器</t>
+  </si>
+  <si>
+    <t>锋龙股份,咸亨国际,泰嘉股份,永和智控,江苏神通,新柴股份,金太阳,中寰股份,正泰电源,冰轮环境</t>
+  </si>
+  <si>
+    <t>江钨装备,神开股份,杰克科技,展鹏科技,兰石重装,长江能科,威领股份,同力天启,电光科技,锡装股份</t>
+  </si>
+  <si>
+    <t>福晶科技,冠捷科技,龙腾光电,深纺织Ａ,同兴达,聚飞光电,华映科技,瑞丰光电,亚世光电,艾比森</t>
   </si>
 </sst>
 </file>
@@ -460,13 +460,13 @@
         <v>16</v>
       </c>
       <c r="D2">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="E2">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="F2">
-        <v>4.05</v>
+        <v>4.8</v>
       </c>
       <c r="G2" t="s">
         <v>21</v>
@@ -483,13 +483,13 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="G3" t="s">
         <v>22</v>
@@ -506,13 +506,13 @@
         <v>18</v>
       </c>
       <c r="D4">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="G4" t="s">
         <v>23</v>
@@ -520,7 +520,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
@@ -529,13 +529,13 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E5">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F5">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="G5" t="s">
         <v>24</v>
@@ -543,7 +543,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
@@ -552,13 +552,13 @@
         <v>20</v>
       </c>
       <c r="D6">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F6">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="G6" t="s">
         <v>25</v>
